--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2018_arica_y_parinacota.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:44</t>
+    <t xml:space="preserve">2026-09-24 00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -588,10 +588,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +605,7 @@
         <v>-0.38</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -619,7 +619,7 @@
         <v>-0.04</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11">
@@ -633,7 +633,7 @@
         <v>0.15</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
